--- a/marketer_forms/017_lip_balm_survey--marketer_forms.xlsx
+++ b/marketer_forms/017_lip_balm_survey--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1245,17 +1245,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>survey_balm_type_choices</t>
+          <t>survey_favourite_balm_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lip_balm_with_spf</t>
+          <t>lip_balm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lip Balm with SPF</t>
+          <t>Lip Balm</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lip_balm</t>
+          <t>lip_gloss</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lip Balm</t>
+          <t>Lip Gloss</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lip_gloss</t>
+          <t>lipstick</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lip Gloss</t>
+          <t>Lipstick</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lipstick</t>
+          <t>lip_balm_with_spf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lipstick</t>
+          <t>Lip Balm with SPF</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lip_balm_with_spf</t>
+          <t>lip_balm_without_spf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lip Balm with SPF</t>
+          <t>Lip Balm without SPF</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lip_balm_without_spf</t>
+          <t>lip_gloss_with_spf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lip Balm without SPF</t>
+          <t>Lip Gloss with SPF</t>
         </is>
       </c>
     </row>
@@ -1352,46 +1352,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lip_gloss_with_spf</t>
+          <t>lipstick_with_spf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lip Gloss with SPF</t>
+          <t>Lipstick with SPF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>survey_favourite_balm_choices</t>
+          <t>survey_important_feature_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lipstick_with_spf</t>
+          <t>moisturizing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lipstick with SPF</t>
+          <t>Moisturizing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>survey_favourite_balm_choices</t>
+          <t>survey_important_feature_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lip_balm_with_spf</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lip Balm with SPF</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>moisturizing</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Moisturizing</t>
+          <t>Protection</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fragrance</t>
+          <t>flavour</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fragrance</t>
+          <t>Flavour</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>protection</t>
+          <t>texture</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Texture</t>
         </is>
       </c>
     </row>
@@ -1454,46 +1454,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>flavour</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Flavour</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>survey_important_feature_choices</t>
+          <t>survey_important_important_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>texture</t>
+          <t>1_-_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Texture</t>
+          <t>1 - 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>survey_important_feature_choices</t>
+          <t>survey_important_important_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>3_-_5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>3 - 5</t>
         </is>
       </c>
     </row>
@@ -1505,80 +1505,80 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1_-_2</t>
+          <t>6_-_8</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1 - 2</t>
+          <t>6 - 8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>survey_important_important_choices</t>
+          <t>survey_would_recommend_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3_-_5</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3 - 5</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>survey_important_important_choices</t>
+          <t>survey_would_recommend_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>6_-_8</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6 - 8</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>survey_would_recommend_choices</t>
+          <t>survey_recommendation_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>lip_balm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Lip Balm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>survey_would_recommend_choices</t>
+          <t>survey_recommendation_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>lip_gloss</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Lip Gloss</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>lip_balm</t>
+          <t>lipstick</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lip Balm</t>
+          <t>Lipstick</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lip_gloss</t>
+          <t>lip_balm_with_spf</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lip Gloss</t>
+          <t>Lip Balm with SPF</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lipstick</t>
+          <t>lip_balm_without_spf</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lipstick</t>
+          <t>Lip Balm without SPF</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lip_balm_with_spf</t>
+          <t>lip_gloss_with_spf</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lip Balm with SPF</t>
+          <t>Lip Gloss with SPF</t>
         </is>
       </c>
     </row>
@@ -1658,63 +1658,63 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lip_balm_without_spf</t>
+          <t>lipstick_with_spf</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lip Balm without SPF</t>
+          <t>Lipstick with SPF</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>survey_recommendation_choices</t>
+          <t>survey_what_else_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lip_gloss_with_spf</t>
+          <t>lip_balm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lip Gloss with SPF</t>
+          <t>Lip Balm</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>survey_recommendation_choices</t>
+          <t>survey_what_else_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lipstick_with_spf</t>
+          <t>lip_gloss</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lipstick with SPF</t>
+          <t>Lip Gloss</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>survey_recommendation_choices</t>
+          <t>survey_what_else_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>lip_balm_with_spf</t>
+          <t>lipstick</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lip Balm with SPF</t>
+          <t>Lipstick</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>lip_balm</t>
+          <t>lip_balm_with_spf</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lip Balm</t>
+          <t>Lip Balm with SPF</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>lip_gloss</t>
+          <t>lip_balm_without_spf</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lip Gloss</t>
+          <t>Lip Balm without SPF</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>lipstick</t>
+          <t>lip_gloss_with_spf</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lipstick</t>
+          <t>Lip Gloss with SPF</t>
         </is>
       </c>
     </row>
@@ -1777,80 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>lip_balm_with_spf</t>
+          <t>lipstick_with_spf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lip Balm with SPF</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>survey_what_else_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>lip_balm_without_spf</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Lip Balm without SPF</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>survey_what_else_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>lip_gloss_with_spf</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Lip Gloss with SPF</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>survey_what_else_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>lipstick_with_spf</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
           <t>Lipstick with SPF</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>survey_what_else_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>lip_balm_with_spf</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Lip Balm with SPF</t>
         </is>
       </c>
     </row>
